--- a/img/RAUI.xlsx
+++ b/img/RAUI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q32468\Desktop\RAUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E26EE15-D994-46B3-8C6A-CCB853FC0FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E0015A-3544-42EB-9BE8-7BAB58F9B09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME" sheetId="1" r:id="rId1"/>
@@ -1150,7 +1150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1163,6 +1163,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1446,19 +1449,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="55.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="55.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5" t="s">
         <v>344</v>
       </c>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>342</v>
       </c>
@@ -1466,7 +1469,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>338</v>
       </c>
@@ -1474,7 +1477,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>336</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>337</v>
       </c>
@@ -1490,7 +1493,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
       <c r="C7" s="2"/>
     </row>
   </sheetData>
@@ -1504,19 +1507,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7E3F19-439F-4BC5-AAD6-B356CF69BB9D}">
   <dimension ref="A1:L325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>324</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>-1.6532293230588</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1630,7 +1633,7 @@
         <v>-1.6977212168256903</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>-1.6254679241171583</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1706,7 +1709,7 @@
         <v>-1.5848649775355601</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>-1.2769058185486881</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1782,7 +1785,7 @@
         <v>-1.1570132319357775</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1820,7 +1823,7 @@
         <v>-1.2947383428293788</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1858,7 +1861,7 @@
         <v>-0.89752768399867355</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>-0.36968564237696233</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1934,7 +1937,7 @@
         <v>-0.29314101179105195</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1972,7 +1975,7 @@
         <v>-0.4805766358889384</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>-0.76718070445336839</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2048,7 +2051,7 @@
         <v>-0.47069248445406631</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2086,7 +2089,7 @@
         <v>-0.38906650869847764</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2124,7 +2127,7 @@
         <v>6.4792267540147802E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>-0.19579248338644489</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2200,7 +2203,7 @@
         <v>-0.28267986422419694</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2238,7 +2241,7 @@
         <v>5.5755583349676223E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2276,7 +2279,7 @@
         <v>0.1146577825085833</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>0.17276223588206577</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2352,7 +2355,7 @@
         <v>1.7303118650617038</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2390,7 +2393,7 @@
         <v>0.76493178423060149</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2428,7 +2431,7 @@
         <v>9.2205339176604575E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>1.1524298147836926E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>0.18863933634234537</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2542,7 +2545,7 @@
         <v>-0.22248802615175484</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -2580,7 +2583,7 @@
         <v>-0.4849181773432264</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2618,7 +2621,7 @@
         <v>-0.32478897313134941</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>-0.70452999582275555</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2694,7 +2697,7 @@
         <v>2.32523308014577E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2732,7 +2735,7 @@
         <v>-0.2954961340878352</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>0.77468375090190533</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2808,7 +2811,7 @@
         <v>0.83215613275921785</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2846,7 +2849,7 @@
         <v>0.65719564655514029</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -2884,7 +2887,7 @@
         <v>-0.11782011179999174</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2922,7 +2925,7 @@
         <v>9.8116203243949804E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>0.35137067321039678</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2998,7 +3001,7 @@
         <v>0.90575084040274478</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -3036,7 +3039,7 @@
         <v>1.2835880367979546</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>0.23667408939636023</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3112,7 +3115,7 @@
         <v>-0.75838505133330836</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>-1.1160589393059703</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3188,7 +3191,7 @@
         <v>-1.0516231763091552</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3226,7 +3229,7 @@
         <v>-0.33851598678866074</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3264,7 +3267,7 @@
         <v>-0.81947988884448397</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3302,7 +3305,7 @@
         <v>-0.86377079495864717</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3340,7 +3343,7 @@
         <v>-0.75092805858120448</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3378,7 +3381,7 @@
         <v>-1.3175034589853514</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>-1.2739710380073408</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3454,7 +3457,7 @@
         <v>-1.342459015091797</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3492,7 +3495,7 @@
         <v>-0.76932882539820346</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -3530,7 +3533,7 @@
         <v>-0.7631336633701542</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -3568,7 +3571,7 @@
         <v>-0.31870160749276089</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>-0.89420054530553783</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -3644,7 +3647,7 @@
         <v>-0.97214166255985113</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -3682,7 +3685,7 @@
         <v>-0.30183794110528217</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -3720,7 +3723,7 @@
         <v>-0.85949382988586687</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -3758,7 +3761,7 @@
         <v>-0.70040330254329441</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -3796,7 +3799,7 @@
         <v>-1.1881141135819671</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -3834,7 +3837,7 @@
         <v>-1.5622285727845262</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -3872,7 +3875,7 @@
         <v>-1.7957663463133453</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -3910,7 +3913,7 @@
         <v>-1.7665349570464139</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>-1.0885035192785022</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -3986,7 +3989,7 @@
         <v>-0.73683096941099102</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4024,7 +4027,7 @@
         <v>-1.1165466457657156</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -4062,7 +4065,7 @@
         <v>-1.0436451281332202</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -4100,7 +4103,7 @@
         <v>-1.6920250327510638</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -4138,7 +4141,7 @@
         <v>-0.80153513829859113</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -4176,7 +4179,7 @@
         <v>-1.1043278473511378</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -4214,7 +4217,7 @@
         <v>-1.0278112102090382</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -4252,7 +4255,7 @@
         <v>-1.4985058361014949</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -4290,7 +4293,7 @@
         <v>-1.3505700958301887</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>-1.146144089421484</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -4366,7 +4369,7 @@
         <v>-1.0037048421951937</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -4404,7 +4407,7 @@
         <v>-1.3274615148062427</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -4442,7 +4445,7 @@
         <v>-0.80079515519358058</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -4480,7 +4483,7 @@
         <v>-0.77988980183483281</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -4518,7 +4521,7 @@
         <v>-1.0204944749438587</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -4556,7 +4559,7 @@
         <v>-0.54485589238927767</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -4594,7 +4597,7 @@
         <v>-0.53785001702411595</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>80</v>
       </c>
@@ -4632,7 +4635,7 @@
         <v>-1.4362002941552017</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -4670,7 +4673,7 @@
         <v>-1.2246778640249403</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>82</v>
       </c>
@@ -4708,7 +4711,7 @@
         <v>-1.1677612057941256</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -4746,7 +4749,7 @@
         <v>-1.3216854494134109</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -4784,7 +4787,7 @@
         <v>-1.2012017381599731</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>85</v>
       </c>
@@ -4822,7 +4825,7 @@
         <v>-1.6924009061152168</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>86</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>-1.2646113846864497</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>87</v>
       </c>
@@ -4898,7 +4901,7 @@
         <v>-1.5144662242486226</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>88</v>
       </c>
@@ -4936,7 +4939,7 @@
         <v>-1.5491751700929632</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>-1.3647537952727393</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>90</v>
       </c>
@@ -5012,7 +5015,7 @@
         <v>-1.1140843218703036</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>91</v>
       </c>
@@ -5050,7 +5053,7 @@
         <v>0.70978951066670326</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>92</v>
       </c>
@@ -5088,7 +5091,7 @@
         <v>0.25707914980244584</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>93</v>
       </c>
@@ -5126,7 +5129,7 @@
         <v>-0.2857612949731112</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -5164,7 +5167,7 @@
         <v>5.8424553328078221E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -5202,7 +5205,7 @@
         <v>0.38497488780914119</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>96</v>
       </c>
@@ -5240,7 +5243,7 @@
         <v>0.94079705364369937</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -5278,7 +5281,7 @@
         <v>0.43692970294681432</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -5316,7 +5319,7 @@
         <v>1.0478211329444773</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -5354,7 +5357,7 @@
         <v>0.92438979559934253</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>0.90138164969120127</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -5430,7 +5433,7 @@
         <v>1.3085727857249871</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -5468,7 +5471,7 @@
         <v>1.8320072016908546</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -5506,7 +5509,7 @@
         <v>2.268392427321976</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -5544,7 +5547,7 @@
         <v>2.0713577835806074</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>1.7736518743650347</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -5620,7 +5623,7 @@
         <v>1.044424474066896</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -5658,7 +5661,7 @@
         <v>1.4905065355692195</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -5696,7 +5699,7 @@
         <v>1.920949713624571</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -5734,7 +5737,7 @@
         <v>1.7916402428675848</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -5772,7 +5775,7 @@
         <v>1.1344723744552161</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -5810,7 +5813,7 @@
         <v>0.57316755007501496</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -5848,7 +5851,7 @@
         <v>0.78670982641905407</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -5886,7 +5889,7 @@
         <v>1.187019354315588</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -5924,7 +5927,7 @@
         <v>0.70957497404994363</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -5962,7 +5965,7 @@
         <v>0.80769574325788807</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -6000,7 +6003,7 @@
         <v>0.77589484556017896</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>117</v>
       </c>
@@ -6038,7 +6041,7 @@
         <v>0.66908824833607106</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -6076,7 +6079,7 @@
         <v>0.33407694241989799</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>119</v>
       </c>
@@ -6114,7 +6117,7 @@
         <v>0.27399136805485846</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>120</v>
       </c>
@@ -6152,7 +6155,7 @@
         <v>1.0045568751741909</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>121</v>
       </c>
@@ -6190,7 +6193,7 @@
         <v>0.88927181972780078</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -6228,7 +6231,7 @@
         <v>0.52955489383960896</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -6266,7 +6269,7 @@
         <v>0.3247921989796736</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>124</v>
       </c>
@@ -6304,7 +6307,7 @@
         <v>1.4327058113488622</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>125</v>
       </c>
@@ -6342,7 +6345,7 @@
         <v>1.4076210746573481</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -6380,7 +6383,7 @@
         <v>0.83362407773073943</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>127</v>
       </c>
@@ -6418,7 +6421,7 @@
         <v>0.91212914197516726</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>128</v>
       </c>
@@ -6456,7 +6459,7 @@
         <v>0.76134618239193397</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -6494,7 +6497,7 @@
         <v>0.86289584625722293</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>130</v>
       </c>
@@ -6532,7 +6535,7 @@
         <v>1.1459930575186916</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>131</v>
       </c>
@@ -6570,7 +6573,7 @@
         <v>0.52355628277795951</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>132</v>
       </c>
@@ -6608,7 +6611,7 @@
         <v>0.74071239976066749</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>133</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>0.92399436531983448</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>134</v>
       </c>
@@ -6684,7 +6687,7 @@
         <v>1.2067618101803106</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -6722,7 +6725,7 @@
         <v>0.85932931707941485</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>136</v>
       </c>
@@ -6760,7 +6763,7 @@
         <v>0.72521189853896662</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>137</v>
       </c>
@@ -6798,7 +6801,7 @@
         <v>1.0951188702850558</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -6836,7 +6839,7 @@
         <v>0.79958904595131275</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -6874,7 +6877,7 @@
         <v>1.8614067911137433</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -6912,7 +6915,7 @@
         <v>1.9017021916970067</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>141</v>
       </c>
@@ -6950,7 +6953,7 @@
         <v>1.4493862200436851</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -6988,7 +6991,7 @@
         <v>1.6483181517123868</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -7026,7 +7029,7 @@
         <v>1.7258310895294229</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>144</v>
       </c>
@@ -7064,7 +7067,7 @@
         <v>1.7350124528945052</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>145</v>
       </c>
@@ -7102,7 +7105,7 @@
         <v>1.7287731105427442</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>146</v>
       </c>
@@ -7140,7 +7143,7 @@
         <v>1.486243422794191</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -7178,7 +7181,7 @@
         <v>1.8132694320900606</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>148</v>
       </c>
@@ -7216,7 +7219,7 @@
         <v>1.5052444578608482</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>149</v>
       </c>
@@ -7254,7 +7257,7 @@
         <v>2.0282403611587054</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>150</v>
       </c>
@@ -7292,7 +7295,7 @@
         <v>2.0919564058944999</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>151</v>
       </c>
@@ -7330,7 +7333,7 @@
         <v>1.9260799550191954</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -7368,7 +7371,7 @@
         <v>1.5123189047013055</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>153</v>
       </c>
@@ -7406,7 +7409,7 @@
         <v>1.3207894449513513</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>154</v>
       </c>
@@ -7444,7 +7447,7 @@
         <v>1.191827388490218</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>155</v>
       </c>
@@ -7482,7 +7485,7 @@
         <v>0.84102419686067675</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -7520,7 +7523,7 @@
         <v>0.68673571705464898</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>157</v>
       </c>
@@ -7558,7 +7561,7 @@
         <v>0.81726208551276014</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>158</v>
       </c>
@@ -7596,7 +7599,7 @@
         <v>0.90339581331874053</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>159</v>
       </c>
@@ -7634,7 +7637,7 @@
         <v>0.89402269449408478</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>160</v>
       </c>
@@ -7672,7 +7675,7 @@
         <v>0.34832727016697768</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>161</v>
       </c>
@@ -7710,7 +7713,7 @@
         <v>0.20530074678231738</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>162</v>
       </c>
@@ -7748,7 +7751,7 @@
         <v>0.49789754431680328</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>163</v>
       </c>
@@ -7786,7 +7789,7 @@
         <v>0.74055533652856376</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>164</v>
       </c>
@@ -7824,7 +7827,7 @@
         <v>-1.5123741935570409E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>165</v>
       </c>
@@ -7862,7 +7865,7 @@
         <v>-0.1291833227767534</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -7900,7 +7903,7 @@
         <v>-0.18038876563166875</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>167</v>
       </c>
@@ -7938,7 +7941,7 @@
         <v>0.261552203700397</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>168</v>
       </c>
@@ -7976,7 +7979,7 @@
         <v>-0.24877225343352552</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>169</v>
       </c>
@@ -8014,7 +8017,7 @@
         <v>-7.3604426137760068E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>170</v>
       </c>
@@ -8052,7 +8055,7 @@
         <v>-5.1357396575339442E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>171</v>
       </c>
@@ -8090,7 +8093,7 @@
         <v>-0.5737632801018715</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>172</v>
       </c>
@@ -8128,7 +8131,7 @@
         <v>-1.0182876847997877</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>173</v>
       </c>
@@ -8166,7 +8169,7 @@
         <v>-1.086844775024701</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>174</v>
       </c>
@@ -8204,7 +8207,7 @@
         <v>-0.65067834406470559</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>175</v>
       </c>
@@ -8242,7 +8245,7 @@
         <v>1.2477527379322371E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>176</v>
       </c>
@@ -8280,7 +8283,7 @@
         <v>-0.39121571315806031</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>177</v>
       </c>
@@ -8318,7 +8321,7 @@
         <v>0.10112187886595884</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -8356,7 +8359,7 @@
         <v>-0.67498885968663946</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>179</v>
       </c>
@@ -8394,7 +8397,7 @@
         <v>-0.54485079538619963</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>180</v>
       </c>
@@ -8432,7 +8435,7 @@
         <v>-1.2172758282498166</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>181</v>
       </c>
@@ -8470,7 +8473,7 @@
         <v>-1.4336314904591416</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>182</v>
       </c>
@@ -8508,7 +8511,7 @@
         <v>-1.1723807475940096</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>183</v>
       </c>
@@ -8546,7 +8549,7 @@
         <v>-1.6029477585126548</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>184</v>
       </c>
@@ -8584,7 +8587,7 @@
         <v>-1.2995737899852027</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>185</v>
       </c>
@@ -8622,7 +8625,7 @@
         <v>-1.0641494188855047</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -8660,7 +8663,7 @@
         <v>-1.428205279070156</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>187</v>
       </c>
@@ -8698,7 +8701,7 @@
         <v>-0.78667198657709925</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -8736,7 +8739,7 @@
         <v>-0.67930113159028527</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -8774,7 +8777,7 @@
         <v>-0.76629287115011602</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -8812,7 +8815,7 @@
         <v>-0.56060266212395637</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>191</v>
       </c>
@@ -8850,7 +8853,7 @@
         <v>-0.61103561789857763</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>192</v>
       </c>
@@ -8888,7 +8891,7 @@
         <v>0.52117648507734093</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>193</v>
       </c>
@@ -8926,7 +8929,7 @@
         <v>0.6753558607531992</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>194</v>
       </c>
@@ -8964,7 +8967,7 @@
         <v>-0.16812650068588789</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -9002,7 +9005,7 @@
         <v>8.7724858237590561E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>196</v>
       </c>
@@ -9040,7 +9043,7 @@
         <v>-8.4793282936343292E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>197</v>
       </c>
@@ -9078,7 +9081,7 @@
         <v>-9.1294798306793407E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -9116,7 +9119,7 @@
         <v>7.4322926347605484E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -9154,7 +9157,7 @@
         <v>-0.52721748320546069</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>200</v>
       </c>
@@ -9192,7 +9195,7 @@
         <v>0.24088667664807956</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>201</v>
       </c>
@@ -9230,7 +9233,7 @@
         <v>-0.27455385558794682</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>202</v>
       </c>
@@ -9268,7 +9271,7 @@
         <v>-0.17295968519958196</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>203</v>
       </c>
@@ -9306,7 +9309,7 @@
         <v>-0.41028659996352085</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>204</v>
       </c>
@@ -9344,7 +9347,7 @@
         <v>-0.37193722041393079</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>205</v>
       </c>
@@ -9382,7 +9385,7 @@
         <v>-0.26953547362437763</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>206</v>
       </c>
@@ -9420,7 +9423,7 @@
         <v>-1.0252053593892074</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>207</v>
       </c>
@@ -9458,7 +9461,7 @@
         <v>-0.83407339118607637</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>208</v>
       </c>
@@ -9496,7 +9499,7 @@
         <v>-1.3487634730963642</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>209</v>
       </c>
@@ -9534,7 +9537,7 @@
         <v>-1.2143228336562524</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>210</v>
       </c>
@@ -9572,7 +9575,7 @@
         <v>-1.6741086574952007</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>211</v>
       </c>
@@ -9610,7 +9613,7 @@
         <v>-1.1793418672837215</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>212</v>
       </c>
@@ -9648,7 +9651,7 @@
         <v>-0.99339215789933644</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>213</v>
       </c>
@@ -9686,7 +9689,7 @@
         <v>-0.6769083547164646</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>214</v>
       </c>
@@ -9724,7 +9727,7 @@
         <v>-0.95592872744456237</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>215</v>
       </c>
@@ -9762,7 +9765,7 @@
         <v>-1.0616427158174757</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>216</v>
       </c>
@@ -9800,7 +9803,7 @@
         <v>-1.4750273724398881</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>217</v>
       </c>
@@ -9838,7 +9841,7 @@
         <v>-0.87285378600285968</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>218</v>
       </c>
@@ -9876,7 +9879,7 @@
         <v>-0.52978838022141839</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>219</v>
       </c>
@@ -9914,7 +9917,7 @@
         <v>-0.70443679114277669</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>220</v>
       </c>
@@ -9952,7 +9955,7 @@
         <v>0.216414950789279</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>221</v>
       </c>
@@ -9990,7 +9993,7 @@
         <v>-3.8109348754945677E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>222</v>
       </c>
@@ -10028,7 +10031,7 @@
         <v>0.11737353048277581</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>223</v>
       </c>
@@ -10066,7 +10069,7 @@
         <v>0.15963838311328135</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>224</v>
       </c>
@@ -10104,7 +10107,7 @@
         <v>0.43481057441466353</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>225</v>
       </c>
@@ -10142,7 +10145,7 @@
         <v>0.64366058656460867</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>226</v>
       </c>
@@ -10180,7 +10183,7 @@
         <v>0.39454992176325815</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>227</v>
       </c>
@@ -10218,7 +10221,7 @@
         <v>7.0317509302066344E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>228</v>
       </c>
@@ -10256,7 +10259,7 @@
         <v>-0.16665596567026505</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>229</v>
       </c>
@@ -10294,7 +10297,7 @@
         <v>6.215454759069057E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>230</v>
       </c>
@@ -10332,7 +10335,7 @@
         <v>-0.16917799102354758</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>231</v>
       </c>
@@ -10370,7 +10373,7 @@
         <v>9.0394405476817999E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>232</v>
       </c>
@@ -10408,7 +10411,7 @@
         <v>0.24797349402118157</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>233</v>
       </c>
@@ -10446,7 +10449,7 @@
         <v>0.10605579909939263</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -10484,7 +10487,7 @@
         <v>0.17624663088220333</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>235</v>
       </c>
@@ -10522,7 +10525,7 @@
         <v>1.8108924197103575</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>236</v>
       </c>
@@ -10560,7 +10563,7 @@
         <v>1.0621864371222798</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>237</v>
       </c>
@@ -10598,7 +10601,7 @@
         <v>0.85066477214351965</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>238</v>
       </c>
@@ -10636,7 +10639,7 @@
         <v>0.23646715508711974</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>239</v>
       </c>
@@ -10674,7 +10677,7 @@
         <v>0.13766428922100374</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>240</v>
       </c>
@@ -10712,7 +10715,7 @@
         <v>0.19149527235009328</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>241</v>
       </c>
@@ -10750,7 +10753,7 @@
         <v>0.7301574429158515</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>242</v>
       </c>
@@ -10788,7 +10791,7 @@
         <v>2.5691831803607887</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>243</v>
       </c>
@@ -10826,7 +10829,7 @@
         <v>2.1712299570951554</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>244</v>
       </c>
@@ -10864,7 +10867,7 @@
         <v>1.8024877900799614</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>245</v>
       </c>
@@ -10902,7 +10905,7 @@
         <v>0.96116579038709526</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>246</v>
       </c>
@@ -10940,7 +10943,7 @@
         <v>0.65823488759540494</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>247</v>
       </c>
@@ -10978,7 +10981,7 @@
         <v>1.0411576850853521</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>248</v>
       </c>
@@ -11016,7 +11019,7 @@
         <v>0.92543775798467254</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>249</v>
       </c>
@@ -11054,7 +11057,7 @@
         <v>0.84401783433095723</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>250</v>
       </c>
@@ -11092,7 +11095,7 @@
         <v>0.16648322100326485</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>251</v>
       </c>
@@ -11130,7 +11133,7 @@
         <v>0.25386324269171257</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>252</v>
       </c>
@@ -11168,7 +11171,7 @@
         <v>0.25008410303186313</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>253</v>
       </c>
@@ -11206,7 +11209,7 @@
         <v>-4.8931846244127788E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>254</v>
       </c>
@@ -11244,7 +11247,7 @@
         <v>3.7282891325478733E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -11282,7 +11285,7 @@
         <v>3.0744819278378825E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>256</v>
       </c>
@@ -11320,7 +11323,7 @@
         <v>-0.24744355838519555</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>257</v>
       </c>
@@ -11358,7 +11361,7 @@
         <v>-0.45632575064791991</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>258</v>
       </c>
@@ -11396,7 +11399,7 @@
         <v>-0.12262620889520463</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>259</v>
       </c>
@@ -11434,7 +11437,7 @@
         <v>0.4181076757305322</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>260</v>
       </c>
@@ -11472,7 +11475,7 @@
         <v>0.8131464139361223</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>261</v>
       </c>
@@ -11510,7 +11513,7 @@
         <v>1.2801279205856475</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>262</v>
       </c>
@@ -11548,7 +11551,7 @@
         <v>1.0709176608485396</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>263</v>
       </c>
@@ -11586,7 +11589,7 @@
         <v>0.47218295293037116</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>264</v>
       </c>
@@ -11624,7 +11627,7 @@
         <v>1.0494357206730631</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>265</v>
       </c>
@@ -11662,7 +11665,7 @@
         <v>1.9280378684417117</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>266</v>
       </c>
@@ -11700,7 +11703,7 @@
         <v>2.8814108536111913</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>267</v>
       </c>
@@ -11738,7 +11741,7 @@
         <v>1.9461995250605795</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>268</v>
       </c>
@@ -11776,7 +11779,7 @@
         <v>1.3370815869261339</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>269</v>
       </c>
@@ -11814,7 +11817,7 @@
         <v>1.5046143877510012</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>270</v>
       </c>
@@ -11852,7 +11855,7 @@
         <v>1.7550664580921371</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>271</v>
       </c>
@@ -11890,7 +11893,7 @@
         <v>1.8614188402280127</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>272</v>
       </c>
@@ -11928,7 +11931,7 @@
         <v>1.5099201341089956</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>273</v>
       </c>
@@ -11966,7 +11969,7 @@
         <v>1.3132348646043552</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>274</v>
       </c>
@@ -12004,7 +12007,7 @@
         <v>0.75592049401970496</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>275</v>
       </c>
@@ -12042,7 +12045,7 @@
         <v>0.56289213818030526</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>276</v>
       </c>
@@ -12080,7 +12083,7 @@
         <v>0.4639481285613809</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>277</v>
       </c>
@@ -12118,7 +12121,7 @@
         <v>0.24787485654507321</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>278</v>
       </c>
@@ -12156,7 +12159,7 @@
         <v>0.78568491402390028</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>279</v>
       </c>
@@ -12194,7 +12197,7 @@
         <v>0.41332186692124578</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>280</v>
       </c>
@@ -12232,7 +12235,7 @@
         <v>0.25224821796821828</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>281</v>
       </c>
@@ -12270,7 +12273,7 @@
         <v>0.10196260163603089</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>282</v>
       </c>
@@ -12308,7 +12311,7 @@
         <v>-0.11265702883503401</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>283</v>
       </c>
@@ -12346,7 +12349,7 @@
         <v>0.67850148919397479</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>284</v>
       </c>
@@ -12384,7 +12387,7 @@
         <v>0.4123228815455437</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>285</v>
       </c>
@@ -12422,7 +12425,7 @@
         <v>0.82042718018154337</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>286</v>
       </c>
@@ -12460,7 +12463,7 @@
         <v>8.2071996646524661E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>287</v>
       </c>
@@ -12498,7 +12501,7 @@
         <v>7.829777830783717E-4</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>288</v>
       </c>
@@ -12536,7 +12539,7 @@
         <v>0.50385144919783542</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>289</v>
       </c>
@@ -12574,7 +12577,7 @@
         <v>-0.22213946456163314</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>290</v>
       </c>
@@ -12612,7 +12615,7 @@
         <v>-0.45425645770463918</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>291</v>
       </c>
@@ -12650,7 +12653,7 @@
         <v>0.11228568140573099</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>292</v>
       </c>
@@ -12688,7 +12691,7 @@
         <v>-0.24738633557434472</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>293</v>
       </c>
@@ -12726,7 +12729,7 @@
         <v>-0.15364543741154629</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>294</v>
       </c>
@@ -12764,7 +12767,7 @@
         <v>-0.33185104310881863</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>295</v>
       </c>
@@ -12802,7 +12805,7 @@
         <v>0.15393299296633117</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>296</v>
       </c>
@@ -12840,7 +12843,7 @@
         <v>-0.23809810021878672</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>297</v>
       </c>
@@ -12878,7 +12881,7 @@
         <v>0.12429449088696566</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>298</v>
       </c>
@@ -12916,7 +12919,7 @@
         <v>0.71393116964869319</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>299</v>
       </c>
@@ -12954,7 +12957,7 @@
         <v>0.17788792716738488</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>300</v>
       </c>
@@ -12992,7 +12995,7 @@
         <v>0.48972663483613749</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>301</v>
       </c>
@@ -13030,7 +13033,7 @@
         <v>0.57748756120606937</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>302</v>
       </c>
@@ -13068,7 +13071,7 @@
         <v>0.93985063771944244</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>303</v>
       </c>
@@ -13106,7 +13109,7 @@
         <v>2.3246178852865742</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>304</v>
       </c>
@@ -13144,7 +13147,7 @@
         <v>0.49622711274638737</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>305</v>
       </c>
@@ -13182,7 +13185,7 @@
         <v>0.86803509061172324</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>306</v>
       </c>
@@ -13220,7 +13223,7 @@
         <v>0.49742289268203493</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>307</v>
       </c>
@@ -13258,7 +13261,7 @@
         <v>0.20372130036436215</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>308</v>
       </c>
@@ -13296,7 +13299,7 @@
         <v>2.7086562985777683E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>309</v>
       </c>
@@ -13334,7 +13337,7 @@
         <v>-0.1524710672186724</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>310</v>
       </c>
@@ -13372,7 +13375,7 @@
         <v>-0.31284529012631224</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>311</v>
       </c>
@@ -13410,7 +13413,7 @@
         <v>-0.41345353277434843</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>312</v>
       </c>
@@ -13448,7 +13451,7 @@
         <v>0.47331287543581041</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>313</v>
       </c>
@@ -13486,7 +13489,7 @@
         <v>-0.16589256223269555</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>314</v>
       </c>
@@ -13524,7 +13527,7 @@
         <v>2.0748955352374496</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>315</v>
       </c>
@@ -13562,87 +13565,197 @@
         <v>1.519687941758874</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>316</v>
       </c>
-      <c r="B318" s="1"/>
-      <c r="C318" s="1"/>
-      <c r="D318" s="1"/>
-      <c r="E318" s="1"/>
-      <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
-      <c r="H318" s="1"/>
-      <c r="I318" s="1"/>
-      <c r="J318" s="1"/>
-      <c r="K318" s="1"/>
-      <c r="L318" s="1"/>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B318" s="1">
+        <v>0.65754385853087449</v>
+      </c>
+      <c r="C318" s="1">
+        <v>1.3291325559068021</v>
+      </c>
+      <c r="D318" s="1">
+        <v>0.86117925968654108</v>
+      </c>
+      <c r="E318" s="1">
+        <v>0.16017595663067072</v>
+      </c>
+      <c r="F318" s="1">
+        <v>1.6928584087492655</v>
+      </c>
+      <c r="G318" s="1">
+        <v>0.81770981978263768</v>
+      </c>
+      <c r="H318" s="1">
+        <v>-0.52993365159761585</v>
+      </c>
+      <c r="I318" s="1">
+        <v>0.43327066661974423</v>
+      </c>
+      <c r="J318" s="1">
+        <v>0.61836427028432761</v>
+      </c>
+      <c r="K318" s="1">
+        <v>0.3613199048393283</v>
+      </c>
+      <c r="L318" s="1">
+        <v>0.92950901556676457</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>317</v>
       </c>
-      <c r="B319" s="1"/>
-      <c r="C319" s="1"/>
-      <c r="D319" s="1"/>
-      <c r="E319" s="1"/>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
-      <c r="H319" s="1"/>
-      <c r="I319" s="1"/>
-      <c r="J319" s="1"/>
-      <c r="K319" s="1"/>
-      <c r="L319" s="1"/>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B319" s="1">
+        <v>0.8833630070178643</v>
+      </c>
+      <c r="C319" s="1">
+        <v>1.214565365208049</v>
+      </c>
+      <c r="D319" s="1">
+        <v>0.24150576573378477</v>
+      </c>
+      <c r="E319" s="1">
+        <v>0.1077875454674533</v>
+      </c>
+      <c r="F319" s="1">
+        <v>1.2470070341726323</v>
+      </c>
+      <c r="G319" s="1">
+        <v>0.73668428938595965</v>
+      </c>
+      <c r="H319" s="1">
+        <v>-1.463514046324462</v>
+      </c>
+      <c r="I319" s="1">
+        <v>0.32148902463980922</v>
+      </c>
+      <c r="J319" s="1">
+        <v>1.5836060823719407</v>
+      </c>
+      <c r="K319" s="1">
+        <v>0.20239748959089321</v>
+      </c>
+      <c r="L319" s="1">
+        <v>0.72389253238134854</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>318</v>
       </c>
-      <c r="B320" s="1"/>
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
-      <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
-      <c r="H320" s="1"/>
-      <c r="I320" s="1"/>
-      <c r="J320" s="1"/>
-      <c r="K320" s="1"/>
-      <c r="L320" s="1"/>
-    </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B320" s="1">
+        <v>1.0425000261054329</v>
+      </c>
+      <c r="C320" s="1">
+        <v>1.3404817515164686</v>
+      </c>
+      <c r="D320" s="1">
+        <v>0.27664419168872956</v>
+      </c>
+      <c r="E320" s="1">
+        <v>5.420697757459552E-2</v>
+      </c>
+      <c r="F320" s="1">
+        <v>1.4374696896801711</v>
+      </c>
+      <c r="G320" s="1">
+        <v>0.72183612391317331</v>
+      </c>
+      <c r="H320" s="1">
+        <v>-1.0705424939885848</v>
+      </c>
+      <c r="I320" s="1">
+        <v>1.085793163508499</v>
+      </c>
+      <c r="J320" s="1">
+        <v>0.33413697296375916</v>
+      </c>
+      <c r="K320" s="1">
+        <v>7.454649094219637E-2</v>
+      </c>
+      <c r="L320" s="1">
+        <v>0.80252057964218282</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>319</v>
       </c>
-      <c r="B321" s="1"/>
-      <c r="C321" s="1"/>
-      <c r="D321" s="1"/>
-      <c r="E321" s="1"/>
-      <c r="F321" s="1"/>
-      <c r="G321" s="1"/>
-      <c r="H321" s="1"/>
-      <c r="I321" s="1"/>
-      <c r="J321" s="1"/>
-      <c r="K321" s="1"/>
-      <c r="L321" s="1"/>
-    </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B321" s="1">
+        <v>1.7082064849055039</v>
+      </c>
+      <c r="C321" s="1">
+        <v>1.623591563220379</v>
+      </c>
+      <c r="D321" s="1">
+        <v>-0.43433970858626914</v>
+      </c>
+      <c r="E321" s="1">
+        <v>0.44056590979595162</v>
+      </c>
+      <c r="F321" s="1">
+        <v>2.0928135715134362</v>
+      </c>
+      <c r="G321" s="1">
+        <v>1.2991050637322821</v>
+      </c>
+      <c r="H321" s="1">
+        <v>-0.70980786013623887</v>
+      </c>
+      <c r="I321" s="1">
+        <v>0.38517448085157446</v>
+      </c>
+      <c r="J321" s="1">
+        <v>-0.47080558084671226</v>
+      </c>
+      <c r="K321" s="1">
+        <v>-9.6590590454880294E-3</v>
+      </c>
+      <c r="L321" s="1">
+        <v>0.92899338048064606</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>320</v>
       </c>
-      <c r="B322" s="1"/>
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
-      <c r="E322" s="1"/>
-      <c r="F322" s="1"/>
-      <c r="G322" s="1"/>
-      <c r="H322" s="1"/>
-      <c r="I322" s="1"/>
-      <c r="J322" s="1"/>
-      <c r="K322" s="1"/>
-      <c r="L322" s="1"/>
-    </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B322" s="1">
+        <v>2.1063134737367704</v>
+      </c>
+      <c r="C322" s="1">
+        <v>1.5904826530588978</v>
+      </c>
+      <c r="D322" s="1">
+        <v>1.0518978837777115</v>
+      </c>
+      <c r="E322" s="1">
+        <v>0.98993541150894437</v>
+      </c>
+      <c r="F322" s="1">
+        <v>3.7897501836194656</v>
+      </c>
+      <c r="G322" s="1">
+        <v>2.0561619184757078</v>
+      </c>
+      <c r="H322" s="1">
+        <v>-0.6802545092057064</v>
+      </c>
+      <c r="I322" s="1">
+        <v>0.27398263833201364</v>
+      </c>
+      <c r="J322" s="1">
+        <v>8.6436480668008547E-2</v>
+      </c>
+      <c r="K322" s="1">
+        <v>1.1408718557173302E-2</v>
+      </c>
+      <c r="L322" s="1">
+        <v>1.6879768177349732</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>321</v>
       </c>
@@ -13658,7 +13771,7 @@
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -13674,7 +13787,7 @@
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>323</v>
       </c>
@@ -13698,20 +13811,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BA72C65-D35F-4D80-8F33-5D8E4EFDAC3E}">
   <dimension ref="A1:L325"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="24.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.54296875" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="10" max="10" width="16.54296875" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>324</v>
       </c>
@@ -13749,7 +13862,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -13787,7 +13900,7 @@
         <v>-1.6532293230588</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -13825,7 +13938,7 @@
         <v>-1.675475269942245</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -13874,7 +13987,7 @@
         <v>-1.6588061546672161</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -13923,7 +14036,7 @@
         <v>-1.636018039492803</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -13972,7 +14085,7 @@
         <v>-1.4957462400671355</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -14021,7 +14134,7 @@
         <v>-1.3395946760066753</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -14070,7 +14183,7 @@
         <v>-1.2428857977712815</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -14119,7 +14232,7 @@
         <v>-1.1164264195879432</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -14168,7 +14281,7 @@
         <v>-0.85398388973500483</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -14217,7 +14330,7 @@
         <v>-0.5201181127222293</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -14266,7 +14379,7 @@
         <v>-0.38113443001898428</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -14315,7 +14428,7 @@
         <v>-0.51363278404445289</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -14364,7 +14477,7 @@
         <v>-0.57281660826545766</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -14413,7 +14526,7 @@
         <v>-0.54231323253530406</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -14462,7 +14575,7 @@
         <v>-0.26498890853746543</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -14511,7 +14624,7 @@
         <v>-0.17335557484825825</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -14560,7 +14673,7 @@
         <v>-0.13789336002349803</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -14609,7 +14722,7 @@
         <v>-0.14090558808698853</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -14658,7 +14771,7 @@
         <v>-3.7422166121979135E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -14707,7 +14820,7 @@
         <v>0.11439186724677509</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -14756,7 +14869,7 @@
         <v>0.67257729448411763</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -14805,7 +14918,7 @@
         <v>0.8893352950581237</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -14854,7 +14967,7 @@
         <v>0.86248299615630319</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -14903,7 +15016,7 @@
         <v>0.28955380718501433</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -14952,7 +15065,7 @@
         <v>9.7456324555595622E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -15001,7 +15114,7 @@
         <v>-7.4414638871908483E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -15050,7 +15163,7 @@
         <v>-0.17292228905087861</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -15099,7 +15212,7 @@
         <v>-0.34406505887544353</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -15148,7 +15261,7 @@
         <v>-0.50474571543244384</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -15197,7 +15310,7 @@
         <v>-0.33535554605088241</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -15246,7 +15359,7 @@
         <v>-0.32559126636971097</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -15295,7 +15408,7 @@
         <v>0.16747998253850929</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -15344,7 +15457,7 @@
         <v>0.43711458319109603</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -15393,7 +15506,7 @@
         <v>0.75467851007208786</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -15442,7 +15555,7 @@
         <v>0.45717722250478876</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -15491,7 +15604,7 @@
         <v>0.21249724599969944</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -15540,7 +15653,7 @@
         <v>0.11055558821811828</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -15589,7 +15702,7 @@
         <v>0.45174590561903044</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -15638,7 +15751,7 @@
         <v>0.84690318347036531</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -15687,7 +15800,7 @@
         <v>0.80867098886568656</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -15736,7 +15849,7 @@
         <v>0.25395902495366879</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -15785,7 +15898,7 @@
         <v>-0.54592330041430615</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -15834,7 +15947,7 @@
         <v>-0.97535572231614465</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -15883,7 +15996,7 @@
         <v>-0.83539936746792876</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -15932,7 +16045,7 @@
         <v>-0.73653968398076664</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -15981,7 +16094,7 @@
         <v>-0.67392222353059728</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -16030,7 +16143,7 @@
         <v>-0.81139291412811188</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -16079,7 +16192,7 @@
         <v>-0.97740077084173438</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -16128,7 +16241,7 @@
         <v>-1.1141341851912989</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -16177,7 +16290,7 @@
         <v>-1.3113111706948297</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -16226,7 +16339,7 @@
         <v>-1.128586292832447</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -16275,7 +16388,7 @@
         <v>-0.95830716795338489</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -16324,7 +16437,7 @@
         <v>-0.61705469875370611</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -16373,7 +16486,7 @@
         <v>-0.65867860538948431</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -16422,7 +16535,7 @@
         <v>-0.72834793845271661</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -16471,7 +16584,7 @@
         <v>-0.72272671632355701</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -16520,7 +16633,7 @@
         <v>-0.71115781118366661</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -16569,7 +16682,7 @@
         <v>-0.62057835784481441</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -16618,7 +16731,7 @@
         <v>-0.91600374867037615</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -16667,7 +16780,7 @@
         <v>-1.1502486629699293</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -16716,7 +16829,7 @@
         <v>-1.5153696775599463</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -16765,7 +16878,7 @@
         <v>-1.7081766253814283</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -16814,7 +16927,7 @@
         <v>-1.5502682742127538</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -16863,7 +16976,7 @@
         <v>-1.1972898152453022</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -16912,7 +17025,7 @@
         <v>-0.9806270448184029</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -16961,7 +17074,7 @@
         <v>-0.96567424776997557</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -17010,7 +17123,7 @@
         <v>-1.2840722688833333</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -17059,7 +17172,7 @@
         <v>-1.1790684330609584</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -17108,7 +17221,7 @@
         <v>-1.1992960061335975</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -17157,7 +17270,7 @@
         <v>-0.97789139861958907</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -17206,7 +17319,7 @@
         <v>-1.2102149645538902</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -17255,7 +17368,7 @@
         <v>-1.2922957140469071</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -17304,7 +17417,7 @@
         <v>-1.3317400071177226</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -17353,7 +17466,7 @@
         <v>-1.1668063424822888</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -17402,7 +17515,7 @@
         <v>-1.1591034821409734</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -17451,7 +17564,7 @@
         <v>-1.0439871707316724</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -17500,7 +17613,7 @@
         <v>-0.96938215727821875</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -17549,7 +17662,7 @@
         <v>-0.8670598106574241</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -17598,7 +17711,7 @@
         <v>-0.78174672305598969</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -17647,7 +17760,7 @@
         <v>-0.70106679478575085</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>80</v>
       </c>
@@ -17696,7 +17809,7 @@
         <v>-0.83963540118953173</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -17745,7 +17858,7 @@
         <v>-1.0662427250680859</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>82</v>
       </c>
@@ -17794,7 +17907,7 @@
         <v>-1.2762131213247558</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -17843,7 +17956,7 @@
         <v>-1.2380415064108254</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -17892,7 +18005,7 @@
         <v>-1.2302161311225033</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>85</v>
       </c>
@@ -17941,7 +18054,7 @@
         <v>-1.4050960312295337</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>86</v>
       </c>
@@ -17990,7 +18103,7 @@
         <v>-1.3860713429872131</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>87</v>
       </c>
@@ -18039,7 +18152,7 @@
         <v>-1.4904928383500964</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>88</v>
       </c>
@@ -18088,7 +18201,7 @@
         <v>-1.4427509263426785</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -18137,7 +18250,7 @@
         <v>-1.4761317298714418</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>90</v>
       </c>
@@ -18186,7 +18299,7 @@
         <v>-1.3426710957453354</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>91</v>
       </c>
@@ -18235,7 +18348,7 @@
         <v>-0.58968286882544652</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>92</v>
       </c>
@@ -18284,7 +18397,7 @@
         <v>-4.9071887133718163E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>93</v>
       </c>
@@ -18333,7 +18446,7 @@
         <v>0.22703578849867931</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -18382,7 +18495,7 @@
         <v>9.9141360524709534E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -18431,7 +18544,7 @@
         <v>5.25460487213694E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>96</v>
       </c>
@@ -18480,7 +18593,7 @@
         <v>0.46139883159363954</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -18529,7 +18642,7 @@
         <v>0.58756721479988494</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -18578,7 +18691,7 @@
         <v>0.80851596317833041</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -18627,7 +18740,7 @@
         <v>0.80304687716354473</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -18676,7 +18789,7 @@
         <v>0.957864192745007</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -18725,7 +18838,7 @@
         <v>1.0447814103385102</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -18774,7 +18887,7 @@
         <v>1.3473205457023478</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -18823,7 +18936,7 @@
         <v>1.802990804912606</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -18872,7 +18985,7 @@
         <v>2.0572524708644795</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -18921,7 +19034,7 @@
         <v>2.037800695089206</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -18970,7 +19083,7 @@
         <v>1.6298113773375127</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -19019,7 +19132,7 @@
         <v>1.4361942946670503</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -19068,7 +19181,7 @@
         <v>1.4852935744202289</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -19117,7 +19230,7 @@
         <v>1.7343654973537916</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -19166,7 +19279,7 @@
         <v>1.615687443649124</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -19215,7 +19328,7 @@
         <v>1.1664267224659386</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -19264,7 +19377,7 @@
         <v>0.83144991698309501</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -19313,7 +19426,7 @@
         <v>0.84896557693655239</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -19362,7 +19475,7 @@
         <v>0.89443471826152854</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -19411,7 +19524,7 @@
         <v>0.90143002387447313</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -19460,7 +19573,7 @@
         <v>0.76438852095600351</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>117</v>
       </c>
@@ -19509,7 +19622,7 @@
         <v>0.75089294571804599</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -19558,7 +19671,7 @@
         <v>0.59302001210538269</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>119</v>
       </c>
@@ -19607,7 +19720,7 @@
         <v>0.4257188529369425</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>120</v>
       </c>
@@ -19656,7 +19769,7 @@
         <v>0.5375417285496491</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>121</v>
       </c>
@@ -19705,7 +19818,7 @@
         <v>0.72260668765228342</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -19754,7 +19867,7 @@
         <v>0.80779452958053355</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -19803,7 +19916,7 @@
         <v>0.58120630418236108</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>124</v>
       </c>
@@ -19852,7 +19965,7 @@
         <v>0.76235096805604829</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>125</v>
       </c>
@@ -19901,7 +20014,7 @@
         <v>1.0550396949952947</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -19950,7 +20063,7 @@
         <v>1.2246503212456499</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>127</v>
       </c>
@@ -19999,7 +20112,7 @@
         <v>1.0511247647877517</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>128</v>
       </c>
@@ -20048,7 +20161,7 @@
         <v>0.83569980069928018</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -20097,7 +20210,7 @@
         <v>0.84545705687477479</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>130</v>
       </c>
@@ -20146,7 +20259,7 @@
         <v>0.92341169538928281</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>131</v>
       </c>
@@ -20195,7 +20308,7 @@
         <v>0.84414839551795795</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>132</v>
       </c>
@@ -20244,7 +20357,7 @@
         <v>0.80342058001910621</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>133</v>
       </c>
@@ -20293,7 +20406,7 @@
         <v>0.72942101595282038</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>134</v>
       </c>
@@ -20342,7 +20455,7 @@
         <v>0.95715619175360411</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -20391,7 +20504,7 @@
         <v>0.9966951641931866</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>136</v>
       </c>
@@ -20440,7 +20553,7 @@
         <v>0.93043434193289742</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>137</v>
       </c>
@@ -20489,7 +20602,7 @@
         <v>0.89322002863447914</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -20538,7 +20651,7 @@
         <v>0.8733066049251117</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -20587,7 +20700,7 @@
         <v>1.2520382357833706</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -20636,7 +20749,7 @@
         <v>1.5208993429206876</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>141</v>
       </c>
@@ -20685,7 +20798,7 @@
         <v>1.7374984009514784</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -20734,7 +20847,7 @@
         <v>1.6664688544843596</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -20783,7 +20896,7 @@
         <v>1.6078451537618317</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>144</v>
       </c>
@@ -20832,7 +20945,7 @@
         <v>1.7030538980454384</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>145</v>
       </c>
@@ -20881,7 +20994,7 @@
         <v>1.7298722176555572</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>146</v>
       </c>
@@ -20930,7 +21043,7 @@
         <v>1.6500096620771467</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -20979,7 +21092,7 @@
         <v>1.6760953218089985</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>148</v>
       </c>
@@ -21028,7 +21141,7 @@
         <v>1.6015857709150332</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>149</v>
       </c>
@@ -21077,7 +21190,7 @@
         <v>1.782251417036538</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>150</v>
       </c>
@@ -21126,7 +21239,7 @@
         <v>1.8751470749713512</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>151</v>
       </c>
@@ -21175,7 +21288,7 @@
         <v>2.0154255740241336</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -21224,7 +21337,7 @@
         <v>1.8434517552050005</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>153</v>
       </c>
@@ -21273,7 +21386,7 @@
         <v>1.5863961015572841</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>154</v>
       </c>
@@ -21322,7 +21435,7 @@
         <v>1.3416452460476249</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>155</v>
       </c>
@@ -21371,7 +21484,7 @@
         <v>1.117880343434082</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -21420,7 +21533,7 @@
         <v>0.90652910080184801</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>157</v>
       </c>
@@ -21469,7 +21582,7 @@
         <v>0.78167399980936203</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>158</v>
       </c>
@@ -21518,7 +21631,7 @@
         <v>0.80246453862871647</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>159</v>
       </c>
@@ -21567,7 +21680,7 @@
         <v>0.87156019777519511</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>160</v>
       </c>
@@ -21616,7 +21729,7 @@
         <v>0.71524859265993435</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>161</v>
       </c>
@@ -21665,7 +21778,7 @@
         <v>0.48255023714779327</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>162</v>
       </c>
@@ -21714,7 +21827,7 @@
         <v>0.35050852042203279</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>163</v>
       </c>
@@ -21763,7 +21876,7 @@
         <v>0.4812512092092282</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>164</v>
       </c>
@@ -21812,7 +21925,7 @@
         <v>0.40777637963659891</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>165</v>
       </c>
@@ -21861,7 +21974,7 @@
         <v>0.19874942393874664</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -21910,7 +22023,7 @@
         <v>-0.10823194344799751</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>167</v>
       </c>
@@ -21959,7 +22072,7 @@
         <v>-1.6006628236008385E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>168</v>
       </c>
@@ -22008,7 +22121,7 @@
         <v>-5.5869605121599088E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>169</v>
       </c>
@@ -22057,7 +22170,7 @@
         <v>-2.0274825290296197E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>170</v>
       </c>
@@ -22106,7 +22219,7 @@
         <v>-0.12457802538220834</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>171</v>
       </c>
@@ -22155,7 +22268,7 @@
         <v>-0.23290836760499034</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>172</v>
       </c>
@@ -22204,7 +22317,7 @@
         <v>-0.54780278715899955</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>173</v>
       </c>
@@ -22253,7 +22366,7 @@
         <v>-0.89296524664211996</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>174</v>
       </c>
@@ -22302,7 +22415,7 @@
         <v>-0.91860360129639818</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>175</v>
       </c>
@@ -22351,7 +22464,7 @@
         <v>-0.57501519723669481</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>176</v>
       </c>
@@ -22400,7 +22513,7 @@
         <v>-0.3431388432811478</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>177</v>
       </c>
@@ -22449,7 +22562,7 @@
         <v>-9.2538768970926347E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -22498,7 +22611,7 @@
         <v>-0.32169423132624697</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>179</v>
       </c>
@@ -22547,7 +22660,7 @@
         <v>-0.37290592540229345</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>180</v>
       </c>
@@ -22596,7 +22709,7 @@
         <v>-0.81237182777421857</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>181</v>
       </c>
@@ -22645,7 +22758,7 @@
         <v>-1.065252704698386</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>182</v>
       </c>
@@ -22694,7 +22807,7 @@
         <v>-1.2744293554343225</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>183</v>
       </c>
@@ -22743,7 +22856,7 @@
         <v>-1.4029866655219354</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>184</v>
       </c>
@@ -22792,7 +22905,7 @@
         <v>-1.3583007653639558</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>185</v>
       </c>
@@ -22841,7 +22954,7 @@
         <v>-1.3222236557944542</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -22890,7 +23003,7 @@
         <v>-1.2639761626469546</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>187</v>
       </c>
@@ -22939,7 +23052,7 @@
         <v>-1.0930088948442533</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -22988,7 +23101,7 @@
         <v>-0.96472613241251359</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -23037,7 +23150,7 @@
         <v>-0.74408866310583355</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -23086,7 +23199,7 @@
         <v>-0.66873222162145252</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>191</v>
       </c>
@@ -23135,7 +23248,7 @@
         <v>-0.64597705039088338</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>192</v>
       </c>
@@ -23184,7 +23297,7 @@
         <v>-0.21682059831506437</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>193</v>
       </c>
@@ -23233,7 +23346,7 @@
         <v>0.19516557597732084</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>194</v>
       </c>
@@ -23282,7 +23395,7 @@
         <v>0.34280194838155076</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -23331,7 +23444,7 @@
         <v>0.19831807276830063</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>196</v>
       </c>
@@ -23380,7 +23493,7 @@
         <v>-5.5064975128213539E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>197</v>
       </c>
@@ -23429,7 +23542,7 @@
         <v>-2.945440766851538E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -23478,7 +23591,7 @@
         <v>-3.39217182985104E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -23527,7 +23640,7 @@
         <v>-0.18139645172154953</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>200</v>
       </c>
@@ -23576,7 +23689,7 @@
         <v>-7.0669293403258546E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>201</v>
       </c>
@@ -23625,7 +23738,7 @@
         <v>-0.18696155404844264</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>202</v>
       </c>
@@ -23674,7 +23787,7 @@
         <v>-6.8875621379816412E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>203</v>
       </c>
@@ -23723,7 +23836,7 @@
         <v>-0.28593338025034987</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>204</v>
       </c>
@@ -23772,7 +23885,7 @@
         <v>-0.31839450185901125</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>205</v>
       </c>
@@ -23821,7 +23934,7 @@
         <v>-0.35058643133394307</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>206</v>
       </c>
@@ -23870,7 +23983,7 @@
         <v>-0.55555935114250532</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>207</v>
       </c>
@@ -23919,7 +24032,7 @@
         <v>-0.70960474139988705</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>208</v>
       </c>
@@ -23968,7 +24081,7 @@
         <v>-1.0693474078905494</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>209</v>
       </c>
@@ -24017,7 +24130,7 @@
         <v>-1.1323865659795642</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>210</v>
       </c>
@@ -24066,7 +24179,7 @@
         <v>-1.412398321415939</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>211</v>
       </c>
@@ -24115,7 +24228,7 @@
         <v>-1.3559244528117249</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>212</v>
       </c>
@@ -24164,7 +24277,7 @@
         <v>-1.2822808942260862</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>213</v>
       </c>
@@ -24213,7 +24326,7 @@
         <v>-0.94988079329984088</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>214</v>
       </c>
@@ -24262,7 +24375,7 @@
         <v>-0.87540974668678784</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>215</v>
       </c>
@@ -24311,7 +24424,7 @@
         <v>-0.89815993265950089</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>216</v>
       </c>
@@ -24360,7 +24473,7 @@
         <v>-1.1641996052339754</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>217</v>
       </c>
@@ -24409,7 +24522,7 @@
         <v>-1.1365079580867412</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>218</v>
       </c>
@@ -24458,7 +24571,7 @@
         <v>-0.95922317955472203</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>219</v>
       </c>
@@ -24507,7 +24620,7 @@
         <v>-0.70235965245568488</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>220</v>
       </c>
@@ -24556,7 +24669,7 @@
         <v>-0.33927007352497207</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>221</v>
       </c>
@@ -24605,7 +24718,7 @@
         <v>-0.17537706303614778</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>222</v>
       </c>
@@ -24654,7 +24767,7 @@
         <v>9.8559710839036377E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>223</v>
       </c>
@@ -24703,7 +24816,7 @@
         <v>7.9634188280370499E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>224</v>
       </c>
@@ -24752,7 +24865,7 @@
         <v>0.23727416267024024</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>225</v>
       </c>
@@ -24801,7 +24914,7 @@
         <v>0.41270318136418455</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>226</v>
       </c>
@@ -24850,7 +24963,7 @@
         <v>0.49100702758084341</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>227</v>
       </c>
@@ -24899,7 +25012,7 @@
         <v>0.36950933920997769</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>228</v>
       </c>
@@ -24948,7 +25061,7 @@
         <v>9.9403821798353123E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>229</v>
       </c>
@@ -24997,7 +25110,7 @@
         <v>-1.139463625916938E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>230</v>
       </c>
@@ -25046,7 +25159,7 @@
         <v>-9.1226469701040688E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>231</v>
       </c>
@@ -25095,7 +25208,7 @@
         <v>-5.5430126520130034E-3</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>232</v>
       </c>
@@ -25144,7 +25257,7 @@
         <v>5.6396636158150659E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>233</v>
       </c>
@@ -25193,7 +25306,7 @@
         <v>0.14814123286579739</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -25242,7 +25355,7 @@
         <v>0.17675864133425914</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>235</v>
       </c>
@@ -25291,7 +25404,7 @@
         <v>0.69773161656398452</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>236</v>
       </c>
@@ -25340,7 +25453,7 @@
         <v>1.0164418292382802</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>237</v>
       </c>
@@ -25389,7 +25502,7 @@
         <v>1.2412478763253858</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>238</v>
       </c>
@@ -25438,7 +25551,7 @@
         <v>0.71643945478430637</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>239</v>
       </c>
@@ -25487,7 +25600,7 @@
         <v>0.40826540548388107</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>240</v>
       </c>
@@ -25536,7 +25649,7 @@
         <v>0.18854223888607224</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>241</v>
       </c>
@@ -25585,7 +25698,7 @@
         <v>0.3531056681623162</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>242</v>
       </c>
@@ -25634,7 +25747,7 @@
         <v>1.1636119652089112</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>243</v>
       </c>
@@ -25683,7 +25796,7 @@
         <v>1.8235235267905985</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>244</v>
       </c>
@@ -25732,7 +25845,7 @@
         <v>2.1809669758453016</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>245</v>
       </c>
@@ -25781,7 +25894,7 @@
         <v>1.6449611791874041</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>246</v>
       </c>
@@ -25830,7 +25943,7 @@
         <v>1.140629489354154</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>247</v>
       </c>
@@ -25879,7 +25992,7 @@
         <v>0.88685278768928411</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>248</v>
       </c>
@@ -25928,7 +26041,7 @@
         <v>0.8749434435551432</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>249</v>
       </c>
@@ -25977,7 +26090,7 @@
         <v>0.93687109246699396</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>250</v>
       </c>
@@ -26026,7 +26139,7 @@
         <v>0.64531293777296483</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>251</v>
       </c>
@@ -26075,7 +26188,7 @@
         <v>0.4214547660086449</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>252</v>
       </c>
@@ -26124,7 +26237,7 @@
         <v>0.2234768555756135</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>253</v>
       </c>
@@ -26173,7 +26286,7 @@
         <v>0.15167183315981597</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>254</v>
       </c>
@@ -26222,7 +26335,7 @@
         <v>7.9478382704404701E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -26271,7 +26384,7 @@
         <v>-2.8581576636037241E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>256</v>
       </c>
@@ -26320,7 +26433,7 @@
         <v>-6.9028728377292972E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>257</v>
       </c>
@@ -26369,7 +26482,7 @@
         <v>-0.23356494236842584</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>258</v>
       </c>
@@ -26418,7 +26531,7 @@
         <v>-0.27546517264277331</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>259</v>
       </c>
@@ -26467,7 +26580,7 @@
         <v>-5.3614761270864099E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>260</v>
       </c>
@@ -26516,7 +26629,7 @@
         <v>0.36954262692381662</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>261</v>
       </c>
@@ -26565,7 +26678,7 @@
         <v>0.83712733675076734</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>262</v>
       </c>
@@ -26614,7 +26727,7 @@
         <v>1.0547306651234365</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>263</v>
       </c>
@@ -26663,7 +26776,7 @@
         <v>0.94107617812151945</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>264</v>
       </c>
@@ -26712,7 +26825,7 @@
         <v>0.86417877815065791</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>265</v>
       </c>
@@ -26761,7 +26874,7 @@
         <v>1.1498855140150486</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>266</v>
       </c>
@@ -26810,7 +26923,7 @@
         <v>1.9529614809086553</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>267</v>
       </c>
@@ -26859,7 +26972,7 @@
         <v>2.2518827490378275</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>268</v>
       </c>
@@ -26908,7 +27021,7 @@
         <v>2.0548973218659685</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>269</v>
       </c>
@@ -26957,7 +27070,7 @@
         <v>1.5959651665792383</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>270</v>
       </c>
@@ -27006,7 +27119,7 @@
         <v>1.5322541442564239</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>271</v>
       </c>
@@ -27055,7 +27168,7 @@
         <v>1.7070332286903838</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>272</v>
       </c>
@@ -27104,7 +27217,7 @@
         <v>1.7088018108097149</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>273</v>
       </c>
@@ -27153,7 +27266,7 @@
         <v>1.5615246129804543</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>274</v>
       </c>
@@ -27202,7 +27315,7 @@
         <v>1.1930251642443519</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>275</v>
       </c>
@@ -27251,7 +27364,7 @@
         <v>0.87734916560145504</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>276</v>
       </c>
@@ -27300,7 +27413,7 @@
         <v>0.59425358692046371</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>277</v>
       </c>
@@ -27349,7 +27462,7 @@
         <v>0.42490504109558641</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>278</v>
       </c>
@@ -27398,7 +27511,7 @@
         <v>0.49916929971011809</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>279</v>
       </c>
@@ -27447,7 +27560,7 @@
         <v>0.48229387916340638</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>280</v>
       </c>
@@ -27496,7 +27609,7 @@
         <v>0.48375166630445482</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>281</v>
       </c>
@@ -27545,7 +27658,7 @@
         <v>0.25584422884183167</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>282</v>
       </c>
@@ -27594,7 +27707,7 @@
         <v>8.0517930256405051E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>283</v>
       </c>
@@ -27643,7 +27756,7 @@
         <v>0.22260235399832387</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>284</v>
       </c>
@@ -27692,7 +27805,7 @@
         <v>0.32605578063482815</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>285</v>
       </c>
@@ -27741,7 +27854,7 @@
         <v>0.63708385030702053</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>286</v>
       </c>
@@ -27790,7 +27903,7 @@
         <v>0.43827401945787053</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>287</v>
       </c>
@@ -27839,7 +27952,7 @@
         <v>0.30109405153704877</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>288</v>
       </c>
@@ -27888,7 +28001,7 @@
         <v>0.19556880787581279</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>289</v>
       </c>
@@ -27937,7 +28050,7 @@
         <v>9.4164987473093542E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>290</v>
       </c>
@@ -27986,7 +28099,7 @@
         <v>-5.7514824356145633E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>291</v>
       </c>
@@ -28035,7 +28148,7 @@
         <v>-0.18803674695351377</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>292</v>
       </c>
@@ -28084,7 +28197,7 @@
         <v>-0.19645237062441764</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>293</v>
       </c>
@@ -28133,7 +28246,7 @@
         <v>-9.6248697193386676E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>294</v>
       </c>
@@ -28182,7 +28295,7 @@
         <v>-0.24429427203156986</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>295</v>
       </c>
@@ -28231,7 +28344,7 @@
         <v>-0.11052116251801125</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>296</v>
       </c>
@@ -28280,7 +28393,7 @@
         <v>-0.13867205012042472</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>297</v>
       </c>
@@ -28329,7 +28442,7 @@
         <v>1.3376461211503371E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>298</v>
       </c>
@@ -28378,7 +28491,7 @@
         <v>0.20004252010562404</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>299</v>
       </c>
@@ -28427,7 +28540,7 @@
         <v>0.33870452923434796</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>300</v>
       </c>
@@ -28476,7 +28589,7 @@
         <v>0.46051524388407183</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>301</v>
       </c>
@@ -28525,7 +28638,7 @@
         <v>0.41503404106986386</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>302</v>
       </c>
@@ -28574,7 +28687,7 @@
         <v>0.66902161125388304</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>303</v>
       </c>
@@ -28623,7 +28736,7 @@
         <v>1.2806520280706952</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>304</v>
       </c>
@@ -28672,7 +28785,7 @@
         <v>1.2535652119174681</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>305</v>
       </c>
@@ -28721,7 +28834,7 @@
         <v>1.229626696214895</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>306</v>
       </c>
@@ -28770,7 +28883,7 @@
         <v>0.62056169868004851</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>307</v>
       </c>
@@ -28819,7 +28932,7 @@
         <v>0.52305976121937336</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>308</v>
       </c>
@@ -28868,7 +28981,7 @@
         <v>0.24274358534405827</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>309</v>
       </c>
@@ -28917,7 +29030,7 @@
         <v>2.6112265377155813E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>310</v>
       </c>
@@ -28966,7 +29079,7 @@
         <v>-0.14607659811973564</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>311</v>
       </c>
@@ -29015,7 +29128,7 @@
         <v>-0.29292329670644435</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>312</v>
       </c>
@@ -29064,7 +29177,7 @@
         <v>-8.4328649154950072E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>313</v>
       </c>
@@ -29113,152 +29226,350 @@
         <v>-3.5344406523744522E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>314</v>
       </c>
-      <c r="B316" s="1">
+      <c r="B316" s="6">
         <f>AVERAGE('RAUI-m'!B314:B316)</f>
         <v>1.6331320864684951</v>
       </c>
-      <c r="C316" s="1">
+      <c r="C316" s="6">
         <f>AVERAGE('RAUI-m'!C314:C316)</f>
         <v>2.2333521809746895</v>
       </c>
-      <c r="D316" s="1">
+      <c r="D316" s="6">
         <f>AVERAGE('RAUI-m'!D314:D316)</f>
         <v>0.73549334535437916</v>
       </c>
-      <c r="E316" s="1">
+      <c r="E316" s="6">
         <f>AVERAGE('RAUI-m'!E314:E316)</f>
         <v>-0.10589350496426768</v>
       </c>
-      <c r="F316" s="1">
+      <c r="F316" s="6">
         <f>AVERAGE('RAUI-m'!F314:F316)</f>
         <v>1.6723292126865721</v>
       </c>
-      <c r="G316" s="1">
+      <c r="G316" s="6">
         <f>AVERAGE('RAUI-m'!G314:G316)</f>
         <v>0.26788211416002522</v>
       </c>
-      <c r="H316" s="1">
+      <c r="H316" s="6">
         <f>AVERAGE('RAUI-m'!H314:H316)</f>
         <v>-1.1095482767539682</v>
       </c>
-      <c r="I316" s="1">
+      <c r="I316" s="6">
         <f>AVERAGE('RAUI-m'!I314:I316)</f>
         <v>0.1085962381896251</v>
       </c>
-      <c r="J316" s="1">
+      <c r="J316" s="6">
         <f>AVERAGE('RAUI-m'!J314:J316)</f>
         <v>0.10890108224288658</v>
       </c>
-      <c r="K316" s="1">
+      <c r="K316" s="6">
         <f>AVERAGE('RAUI-m'!K314:K316)</f>
         <v>-0.12695653794822789</v>
       </c>
-      <c r="L316" s="1">
+      <c r="L316" s="6">
         <f>AVERAGE('RAUI-m'!L314:L316)</f>
         <v>0.79410528281352155</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>315</v>
       </c>
-      <c r="B317" s="1"/>
-      <c r="C317" s="1"/>
-      <c r="D317" s="1"/>
-      <c r="E317" s="1"/>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
-      <c r="H317" s="1"/>
-      <c r="I317" s="1"/>
-      <c r="J317" s="1"/>
-      <c r="K317" s="1"/>
-      <c r="L317" s="1"/>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B317" s="6">
+        <f>AVERAGE('RAUI-m'!B315:B317)</f>
+        <v>1.5803744954402752</v>
+      </c>
+      <c r="C317" s="6">
+        <f>AVERAGE('RAUI-m'!C315:C317)</f>
+        <v>1.8030990067099999</v>
+      </c>
+      <c r="D317" s="6">
+        <f>AVERAGE('RAUI-m'!D315:D317)</f>
+        <v>1.0022065099432609</v>
+      </c>
+      <c r="E317" s="6">
+        <f>AVERAGE('RAUI-m'!E315:E317)</f>
+        <v>6.1862545232614995E-2</v>
+      </c>
+      <c r="F317" s="6">
+        <f>AVERAGE('RAUI-m'!F315:F317)</f>
+        <v>2.9575688080417337</v>
+      </c>
+      <c r="G317" s="6">
+        <f>AVERAGE('RAUI-m'!G315:G317)</f>
+        <v>0.86071297804698543</v>
+      </c>
+      <c r="H317" s="6">
+        <f>AVERAGE('RAUI-m'!H315:H317)</f>
+        <v>-0.80488439330399819</v>
+      </c>
+      <c r="I317" s="6">
+        <f>AVERAGE('RAUI-m'!I315:I317)</f>
+        <v>-5.8488361531445245E-2</v>
+      </c>
+      <c r="J317" s="6">
+        <f>AVERAGE('RAUI-m'!J315:J317)</f>
+        <v>0.31948971393878961</v>
+      </c>
+      <c r="K317" s="6">
+        <f>AVERAGE('RAUI-m'!K315:K317)</f>
+        <v>0.11996457223871337</v>
+      </c>
+      <c r="L317" s="6">
+        <f>AVERAGE('RAUI-m'!L315:L317)</f>
+        <v>1.1428969715878761</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>316</v>
       </c>
-      <c r="B318" s="1"/>
-      <c r="C318" s="1"/>
-      <c r="D318" s="1"/>
-      <c r="E318" s="1"/>
-      <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
-      <c r="H318" s="1"/>
-      <c r="I318" s="1"/>
-      <c r="J318" s="1"/>
-      <c r="K318" s="1"/>
-      <c r="L318" s="1"/>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B318" s="6">
+        <f>AVERAGE('RAUI-m'!B316:B318)</f>
+        <v>1.5334787280827535</v>
+      </c>
+      <c r="C318" s="6">
+        <f>AVERAGE('RAUI-m'!C316:C318)</f>
+        <v>1.6452518301144021</v>
+      </c>
+      <c r="D318" s="6">
+        <f>AVERAGE('RAUI-m'!D316:D318)</f>
+        <v>1.1928542034548097</v>
+      </c>
+      <c r="E318" s="6">
+        <f>AVERAGE('RAUI-m'!E316:E318)</f>
+        <v>0.30057385492116362</v>
+      </c>
+      <c r="F318" s="6">
+        <f>AVERAGE('RAUI-m'!F316:F318)</f>
+        <v>3.6636993139198015</v>
+      </c>
+      <c r="G318" s="6">
+        <f>AVERAGE('RAUI-m'!G316:G318)</f>
+        <v>1.390555414740841</v>
+      </c>
+      <c r="H318" s="6">
+        <f>AVERAGE('RAUI-m'!H316:H318)</f>
+        <v>-0.42292225953894014</v>
+      </c>
+      <c r="I318" s="6">
+        <f>AVERAGE('RAUI-m'!I316:I318)</f>
+        <v>0.10551561540777234</v>
+      </c>
+      <c r="J318" s="6">
+        <f>AVERAGE('RAUI-m'!J316:J318)</f>
+        <v>0.55479503015618847</v>
+      </c>
+      <c r="K318" s="6">
+        <f>AVERAGE('RAUI-m'!K316:K318)</f>
+        <v>0.34207324882050649</v>
+      </c>
+      <c r="L318" s="6">
+        <f>AVERAGE('RAUI-m'!L316:L318)</f>
+        <v>1.5080308308543626</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>317</v>
       </c>
-      <c r="B319" s="1"/>
-      <c r="C319" s="1"/>
-      <c r="D319" s="1"/>
-      <c r="E319" s="1"/>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
-      <c r="H319" s="1"/>
-      <c r="I319" s="1"/>
-      <c r="J319" s="1"/>
-      <c r="K319" s="1"/>
-      <c r="L319" s="1"/>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B319" s="6">
+        <f>AVERAGE('RAUI-m'!B317:B319)</f>
+        <v>0.99697157380938606</v>
+      </c>
+      <c r="C319" s="6">
+        <f>AVERAGE('RAUI-m'!C317:C319)</f>
+        <v>1.3735491530957704</v>
+      </c>
+      <c r="D319" s="6">
+        <f>AVERAGE('RAUI-m'!D317:D319)</f>
+        <v>0.72553319067176691</v>
+      </c>
+      <c r="E319" s="6">
+        <f>AVERAGE('RAUI-m'!E317:E319)</f>
+        <v>0.13044488148795488</v>
+      </c>
+      <c r="F319" s="6">
+        <f>AVERAGE('RAUI-m'!F317:F319)</f>
+        <v>2.1857890965458786</v>
+      </c>
+      <c r="G319" s="6">
+        <f>AVERAGE('RAUI-m'!G317:G319)</f>
+        <v>0.9977543112059184</v>
+      </c>
+      <c r="H319" s="6">
+        <f>AVERAGE('RAUI-m'!H317:H319)</f>
+        <v>-0.62151248269624426</v>
+      </c>
+      <c r="I319" s="6">
+        <f>AVERAGE('RAUI-m'!I317:I319)</f>
+        <v>0.21520241468592358</v>
+      </c>
+      <c r="J319" s="6">
+        <f>AVERAGE('RAUI-m'!J317:J319)</f>
+        <v>0.96744200737884045</v>
+      </c>
+      <c r="K319" s="6">
+        <f>AVERAGE('RAUI-m'!K317:K319)</f>
+        <v>0.33085573377387001</v>
+      </c>
+      <c r="L319" s="6">
+        <f>AVERAGE('RAUI-m'!L317:L319)</f>
+        <v>1.0576964965689957</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>318</v>
       </c>
-      <c r="B320" s="1"/>
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
-      <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
-      <c r="H320" s="1"/>
-      <c r="I320" s="1"/>
-      <c r="J320" s="1"/>
-      <c r="K320" s="1"/>
-      <c r="L320" s="1"/>
-    </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B320" s="6">
+        <f>AVERAGE('RAUI-m'!B318:B320)</f>
+        <v>0.86113563055139064</v>
+      </c>
+      <c r="C320" s="6">
+        <f>AVERAGE('RAUI-m'!C318:C320)</f>
+        <v>1.2947265575437732</v>
+      </c>
+      <c r="D320" s="6">
+        <f>AVERAGE('RAUI-m'!D318:D320)</f>
+        <v>0.45977640570301848</v>
+      </c>
+      <c r="E320" s="6">
+        <f>AVERAGE('RAUI-m'!E318:E320)</f>
+        <v>0.10739015989090651</v>
+      </c>
+      <c r="F320" s="6">
+        <f>AVERAGE('RAUI-m'!F318:F320)</f>
+        <v>1.4591117108673561</v>
+      </c>
+      <c r="G320" s="6">
+        <f>AVERAGE('RAUI-m'!G318:G320)</f>
+        <v>0.75874341102725695</v>
+      </c>
+      <c r="H320" s="6">
+        <f>AVERAGE('RAUI-m'!H318:H320)</f>
+        <v>-1.021330063970221</v>
+      </c>
+      <c r="I320" s="6">
+        <f>AVERAGE('RAUI-m'!I318:I320)</f>
+        <v>0.61351761825601747</v>
+      </c>
+      <c r="J320" s="6">
+        <f>AVERAGE('RAUI-m'!J318:J320)</f>
+        <v>0.84536910854000924</v>
+      </c>
+      <c r="K320" s="6">
+        <f>AVERAGE('RAUI-m'!K318:K320)</f>
+        <v>0.21275462845747262</v>
+      </c>
+      <c r="L320" s="6">
+        <f>AVERAGE('RAUI-m'!L318:L320)</f>
+        <v>0.81864070919676524</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>319</v>
       </c>
-      <c r="B321" s="1"/>
-      <c r="C321" s="1"/>
-      <c r="D321" s="1"/>
-      <c r="E321" s="1"/>
-      <c r="F321" s="1"/>
-      <c r="G321" s="1"/>
-      <c r="H321" s="1"/>
-      <c r="I321" s="1"/>
-      <c r="J321" s="1"/>
-      <c r="K321" s="1"/>
-      <c r="L321" s="1"/>
-    </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B321" s="6">
+        <f>AVERAGE('RAUI-m'!B319:B321)</f>
+        <v>1.2113565060096003</v>
+      </c>
+      <c r="C321" s="6">
+        <f>AVERAGE('RAUI-m'!C319:C321)</f>
+        <v>1.3928795599816322</v>
+      </c>
+      <c r="D321" s="6">
+        <f>AVERAGE('RAUI-m'!D319:D321)</f>
+        <v>2.793674961208174E-2</v>
+      </c>
+      <c r="E321" s="6">
+        <f>AVERAGE('RAUI-m'!E319:E321)</f>
+        <v>0.20085347761266681</v>
+      </c>
+      <c r="F321" s="6">
+        <f>AVERAGE('RAUI-m'!F319:F321)</f>
+        <v>1.5924300984554132</v>
+      </c>
+      <c r="G321" s="6">
+        <f>AVERAGE('RAUI-m'!G319:G321)</f>
+        <v>0.91920849234380508</v>
+      </c>
+      <c r="H321" s="6">
+        <f>AVERAGE('RAUI-m'!H319:H321)</f>
+        <v>-1.0812881334830953</v>
+      </c>
+      <c r="I321" s="6">
+        <f>AVERAGE('RAUI-m'!I319:I321)</f>
+        <v>0.59748555633329425</v>
+      </c>
+      <c r="J321" s="6">
+        <f>AVERAGE('RAUI-m'!J319:J321)</f>
+        <v>0.48231249149632921</v>
+      </c>
+      <c r="K321" s="6">
+        <f>AVERAGE('RAUI-m'!K319:K321)</f>
+        <v>8.9094973829200508E-2</v>
+      </c>
+      <c r="L321" s="6">
+        <f>AVERAGE('RAUI-m'!L319:L321)</f>
+        <v>0.81846883083472577</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>320</v>
       </c>
-      <c r="B322" s="1"/>
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
-      <c r="E322" s="1"/>
-      <c r="F322" s="1"/>
-      <c r="G322" s="1"/>
-      <c r="H322" s="1"/>
-      <c r="I322" s="1"/>
-      <c r="J322" s="1"/>
-      <c r="K322" s="1"/>
-      <c r="L322" s="1"/>
-    </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B322" s="6">
+        <f>AVERAGE('RAUI-m'!B320:B322)</f>
+        <v>1.6190066615825689</v>
+      </c>
+      <c r="C322" s="6">
+        <f>AVERAGE('RAUI-m'!C320:C322)</f>
+        <v>1.5181853225985817</v>
+      </c>
+      <c r="D322" s="6">
+        <f>AVERAGE('RAUI-m'!D320:D322)</f>
+        <v>0.29806745562672399</v>
+      </c>
+      <c r="E322" s="6">
+        <f>AVERAGE('RAUI-m'!E320:E322)</f>
+        <v>0.49490276629316382</v>
+      </c>
+      <c r="F322" s="6">
+        <f>AVERAGE('RAUI-m'!F320:F322)</f>
+        <v>2.4400111482710241</v>
+      </c>
+      <c r="G322" s="6">
+        <f>AVERAGE('RAUI-m'!G320:G322)</f>
+        <v>1.3590343687070543</v>
+      </c>
+      <c r="H322" s="6">
+        <f>AVERAGE('RAUI-m'!H320:H322)</f>
+        <v>-0.82020162111017658</v>
+      </c>
+      <c r="I322" s="6">
+        <f>AVERAGE('RAUI-m'!I320:I322)</f>
+        <v>0.58165009423069569</v>
+      </c>
+      <c r="J322" s="6">
+        <f>AVERAGE('RAUI-m'!J320:J322)</f>
+        <v>-1.6744042404981518E-2</v>
+      </c>
+      <c r="K322" s="6">
+        <f>AVERAGE('RAUI-m'!K320:K322)</f>
+        <v>2.5432050151293881E-2</v>
+      </c>
+      <c r="L322" s="6">
+        <f>AVERAGE('RAUI-m'!L320:L322)</f>
+        <v>1.139830259285934</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>321</v>
       </c>
@@ -29274,7 +29585,7 @@
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -29290,7 +29601,7 @@
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>323</v>
       </c>

--- a/img/RAUI.xlsx
+++ b/img/RAUI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q32468\Desktop\RAUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E0015A-3544-42EB-9BE8-7BAB58F9B09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D344BCBA-78B4-4A32-8C87-787567662D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME" sheetId="1" r:id="rId1"/>
@@ -1150,7 +1150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1163,9 +1163,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -13722,37 +13719,37 @@
         <v>320</v>
       </c>
       <c r="B322" s="1">
-        <v>2.1063134737367704</v>
+        <v>1.3608185809433169</v>
       </c>
       <c r="C322" s="1">
-        <v>1.5904826530588978</v>
+        <v>1.1600954149263996</v>
       </c>
       <c r="D322" s="1">
-        <v>1.0518978837777115</v>
+        <v>0.76244034166375163</v>
       </c>
       <c r="E322" s="1">
-        <v>0.98993541150894437</v>
+        <v>0.63592311247505029</v>
       </c>
       <c r="F322" s="1">
-        <v>3.7897501836194656</v>
+        <v>3.6269999145778109</v>
       </c>
       <c r="G322" s="1">
-        <v>2.0561619184757078</v>
+        <v>2.019144352322646</v>
       </c>
       <c r="H322" s="1">
-        <v>-0.6802545092057064</v>
+        <v>-1.2174341477984139</v>
       </c>
       <c r="I322" s="1">
-        <v>0.27398263833201364</v>
+        <v>0.29499150158962339</v>
       </c>
       <c r="J322" s="1">
-        <v>8.6436480668008547E-2</v>
+        <v>2.7475963077250469</v>
       </c>
       <c r="K322" s="1">
-        <v>1.1408718557173302E-2</v>
+        <v>0.12537876160681544</v>
       </c>
       <c r="L322" s="1">
-        <v>1.6879768177349732</v>
+        <v>1.6553114658566088</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.35">
@@ -29230,47 +29227,47 @@
       <c r="A316" t="s">
         <v>314</v>
       </c>
-      <c r="B316" s="6">
+      <c r="B316" s="1">
         <f>AVERAGE('RAUI-m'!B314:B316)</f>
         <v>1.6331320864684951</v>
       </c>
-      <c r="C316" s="6">
+      <c r="C316" s="1">
         <f>AVERAGE('RAUI-m'!C314:C316)</f>
         <v>2.2333521809746895</v>
       </c>
-      <c r="D316" s="6">
+      <c r="D316" s="1">
         <f>AVERAGE('RAUI-m'!D314:D316)</f>
         <v>0.73549334535437916</v>
       </c>
-      <c r="E316" s="6">
+      <c r="E316" s="1">
         <f>AVERAGE('RAUI-m'!E314:E316)</f>
         <v>-0.10589350496426768</v>
       </c>
-      <c r="F316" s="6">
+      <c r="F316" s="1">
         <f>AVERAGE('RAUI-m'!F314:F316)</f>
         <v>1.6723292126865721</v>
       </c>
-      <c r="G316" s="6">
+      <c r="G316" s="1">
         <f>AVERAGE('RAUI-m'!G314:G316)</f>
         <v>0.26788211416002522</v>
       </c>
-      <c r="H316" s="6">
+      <c r="H316" s="1">
         <f>AVERAGE('RAUI-m'!H314:H316)</f>
         <v>-1.1095482767539682</v>
       </c>
-      <c r="I316" s="6">
+      <c r="I316" s="1">
         <f>AVERAGE('RAUI-m'!I314:I316)</f>
         <v>0.1085962381896251</v>
       </c>
-      <c r="J316" s="6">
+      <c r="J316" s="1">
         <f>AVERAGE('RAUI-m'!J314:J316)</f>
         <v>0.10890108224288658</v>
       </c>
-      <c r="K316" s="6">
+      <c r="K316" s="1">
         <f>AVERAGE('RAUI-m'!K314:K316)</f>
         <v>-0.12695653794822789</v>
       </c>
-      <c r="L316" s="6">
+      <c r="L316" s="1">
         <f>AVERAGE('RAUI-m'!L314:L316)</f>
         <v>0.79410528281352155</v>
       </c>
@@ -29279,47 +29276,47 @@
       <c r="A317" t="s">
         <v>315</v>
       </c>
-      <c r="B317" s="6">
+      <c r="B317" s="1">
         <f>AVERAGE('RAUI-m'!B315:B317)</f>
         <v>1.5803744954402752</v>
       </c>
-      <c r="C317" s="6">
+      <c r="C317" s="1">
         <f>AVERAGE('RAUI-m'!C315:C317)</f>
         <v>1.8030990067099999</v>
       </c>
-      <c r="D317" s="6">
+      <c r="D317" s="1">
         <f>AVERAGE('RAUI-m'!D315:D317)</f>
         <v>1.0022065099432609</v>
       </c>
-      <c r="E317" s="6">
+      <c r="E317" s="1">
         <f>AVERAGE('RAUI-m'!E315:E317)</f>
         <v>6.1862545232614995E-2</v>
       </c>
-      <c r="F317" s="6">
+      <c r="F317" s="1">
         <f>AVERAGE('RAUI-m'!F315:F317)</f>
         <v>2.9575688080417337</v>
       </c>
-      <c r="G317" s="6">
+      <c r="G317" s="1">
         <f>AVERAGE('RAUI-m'!G315:G317)</f>
         <v>0.86071297804698543</v>
       </c>
-      <c r="H317" s="6">
+      <c r="H317" s="1">
         <f>AVERAGE('RAUI-m'!H315:H317)</f>
         <v>-0.80488439330399819</v>
       </c>
-      <c r="I317" s="6">
+      <c r="I317" s="1">
         <f>AVERAGE('RAUI-m'!I315:I317)</f>
         <v>-5.8488361531445245E-2</v>
       </c>
-      <c r="J317" s="6">
+      <c r="J317" s="1">
         <f>AVERAGE('RAUI-m'!J315:J317)</f>
         <v>0.31948971393878961</v>
       </c>
-      <c r="K317" s="6">
+      <c r="K317" s="1">
         <f>AVERAGE('RAUI-m'!K315:K317)</f>
         <v>0.11996457223871337</v>
       </c>
-      <c r="L317" s="6">
+      <c r="L317" s="1">
         <f>AVERAGE('RAUI-m'!L315:L317)</f>
         <v>1.1428969715878761</v>
       </c>
@@ -29328,47 +29325,47 @@
       <c r="A318" t="s">
         <v>316</v>
       </c>
-      <c r="B318" s="6">
+      <c r="B318" s="1">
         <f>AVERAGE('RAUI-m'!B316:B318)</f>
         <v>1.5334787280827535</v>
       </c>
-      <c r="C318" s="6">
+      <c r="C318" s="1">
         <f>AVERAGE('RAUI-m'!C316:C318)</f>
         <v>1.6452518301144021</v>
       </c>
-      <c r="D318" s="6">
+      <c r="D318" s="1">
         <f>AVERAGE('RAUI-m'!D316:D318)</f>
         <v>1.1928542034548097</v>
       </c>
-      <c r="E318" s="6">
+      <c r="E318" s="1">
         <f>AVERAGE('RAUI-m'!E316:E318)</f>
         <v>0.30057385492116362</v>
       </c>
-      <c r="F318" s="6">
+      <c r="F318" s="1">
         <f>AVERAGE('RAUI-m'!F316:F318)</f>
         <v>3.6636993139198015</v>
       </c>
-      <c r="G318" s="6">
+      <c r="G318" s="1">
         <f>AVERAGE('RAUI-m'!G316:G318)</f>
         <v>1.390555414740841</v>
       </c>
-      <c r="H318" s="6">
+      <c r="H318" s="1">
         <f>AVERAGE('RAUI-m'!H316:H318)</f>
         <v>-0.42292225953894014</v>
       </c>
-      <c r="I318" s="6">
+      <c r="I318" s="1">
         <f>AVERAGE('RAUI-m'!I316:I318)</f>
         <v>0.10551561540777234</v>
       </c>
-      <c r="J318" s="6">
+      <c r="J318" s="1">
         <f>AVERAGE('RAUI-m'!J316:J318)</f>
         <v>0.55479503015618847</v>
       </c>
-      <c r="K318" s="6">
+      <c r="K318" s="1">
         <f>AVERAGE('RAUI-m'!K316:K318)</f>
         <v>0.34207324882050649</v>
       </c>
-      <c r="L318" s="6">
+      <c r="L318" s="1">
         <f>AVERAGE('RAUI-m'!L316:L318)</f>
         <v>1.5080308308543626</v>
       </c>
@@ -29377,47 +29374,47 @@
       <c r="A319" t="s">
         <v>317</v>
       </c>
-      <c r="B319" s="6">
+      <c r="B319" s="1">
         <f>AVERAGE('RAUI-m'!B317:B319)</f>
         <v>0.99697157380938606</v>
       </c>
-      <c r="C319" s="6">
+      <c r="C319" s="1">
         <f>AVERAGE('RAUI-m'!C317:C319)</f>
         <v>1.3735491530957704</v>
       </c>
-      <c r="D319" s="6">
+      <c r="D319" s="1">
         <f>AVERAGE('RAUI-m'!D317:D319)</f>
         <v>0.72553319067176691</v>
       </c>
-      <c r="E319" s="6">
+      <c r="E319" s="1">
         <f>AVERAGE('RAUI-m'!E317:E319)</f>
         <v>0.13044488148795488</v>
       </c>
-      <c r="F319" s="6">
+      <c r="F319" s="1">
         <f>AVERAGE('RAUI-m'!F317:F319)</f>
         <v>2.1857890965458786</v>
       </c>
-      <c r="G319" s="6">
+      <c r="G319" s="1">
         <f>AVERAGE('RAUI-m'!G317:G319)</f>
         <v>0.9977543112059184</v>
       </c>
-      <c r="H319" s="6">
+      <c r="H319" s="1">
         <f>AVERAGE('RAUI-m'!H317:H319)</f>
         <v>-0.62151248269624426</v>
       </c>
-      <c r="I319" s="6">
+      <c r="I319" s="1">
         <f>AVERAGE('RAUI-m'!I317:I319)</f>
         <v>0.21520241468592358</v>
       </c>
-      <c r="J319" s="6">
+      <c r="J319" s="1">
         <f>AVERAGE('RAUI-m'!J317:J319)</f>
         <v>0.96744200737884045</v>
       </c>
-      <c r="K319" s="6">
+      <c r="K319" s="1">
         <f>AVERAGE('RAUI-m'!K317:K319)</f>
         <v>0.33085573377387001</v>
       </c>
-      <c r="L319" s="6">
+      <c r="L319" s="1">
         <f>AVERAGE('RAUI-m'!L317:L319)</f>
         <v>1.0576964965689957</v>
       </c>
@@ -29426,47 +29423,47 @@
       <c r="A320" t="s">
         <v>318</v>
       </c>
-      <c r="B320" s="6">
+      <c r="B320" s="1">
         <f>AVERAGE('RAUI-m'!B318:B320)</f>
         <v>0.86113563055139064</v>
       </c>
-      <c r="C320" s="6">
+      <c r="C320" s="1">
         <f>AVERAGE('RAUI-m'!C318:C320)</f>
         <v>1.2947265575437732</v>
       </c>
-      <c r="D320" s="6">
+      <c r="D320" s="1">
         <f>AVERAGE('RAUI-m'!D318:D320)</f>
         <v>0.45977640570301848</v>
       </c>
-      <c r="E320" s="6">
+      <c r="E320" s="1">
         <f>AVERAGE('RAUI-m'!E318:E320)</f>
         <v>0.10739015989090651</v>
       </c>
-      <c r="F320" s="6">
+      <c r="F320" s="1">
         <f>AVERAGE('RAUI-m'!F318:F320)</f>
         <v>1.4591117108673561</v>
       </c>
-      <c r="G320" s="6">
+      <c r="G320" s="1">
         <f>AVERAGE('RAUI-m'!G318:G320)</f>
         <v>0.75874341102725695</v>
       </c>
-      <c r="H320" s="6">
+      <c r="H320" s="1">
         <f>AVERAGE('RAUI-m'!H318:H320)</f>
         <v>-1.021330063970221</v>
       </c>
-      <c r="I320" s="6">
+      <c r="I320" s="1">
         <f>AVERAGE('RAUI-m'!I318:I320)</f>
         <v>0.61351761825601747</v>
       </c>
-      <c r="J320" s="6">
+      <c r="J320" s="1">
         <f>AVERAGE('RAUI-m'!J318:J320)</f>
         <v>0.84536910854000924</v>
       </c>
-      <c r="K320" s="6">
+      <c r="K320" s="1">
         <f>AVERAGE('RAUI-m'!K318:K320)</f>
         <v>0.21275462845747262</v>
       </c>
-      <c r="L320" s="6">
+      <c r="L320" s="1">
         <f>AVERAGE('RAUI-m'!L318:L320)</f>
         <v>0.81864070919676524</v>
       </c>
@@ -29475,47 +29472,47 @@
       <c r="A321" t="s">
         <v>319</v>
       </c>
-      <c r="B321" s="6">
+      <c r="B321" s="1">
         <f>AVERAGE('RAUI-m'!B319:B321)</f>
         <v>1.2113565060096003</v>
       </c>
-      <c r="C321" s="6">
+      <c r="C321" s="1">
         <f>AVERAGE('RAUI-m'!C319:C321)</f>
         <v>1.3928795599816322</v>
       </c>
-      <c r="D321" s="6">
+      <c r="D321" s="1">
         <f>AVERAGE('RAUI-m'!D319:D321)</f>
         <v>2.793674961208174E-2</v>
       </c>
-      <c r="E321" s="6">
+      <c r="E321" s="1">
         <f>AVERAGE('RAUI-m'!E319:E321)</f>
         <v>0.20085347761266681</v>
       </c>
-      <c r="F321" s="6">
+      <c r="F321" s="1">
         <f>AVERAGE('RAUI-m'!F319:F321)</f>
         <v>1.5924300984554132</v>
       </c>
-      <c r="G321" s="6">
+      <c r="G321" s="1">
         <f>AVERAGE('RAUI-m'!G319:G321)</f>
         <v>0.91920849234380508</v>
       </c>
-      <c r="H321" s="6">
+      <c r="H321" s="1">
         <f>AVERAGE('RAUI-m'!H319:H321)</f>
         <v>-1.0812881334830953</v>
       </c>
-      <c r="I321" s="6">
+      <c r="I321" s="1">
         <f>AVERAGE('RAUI-m'!I319:I321)</f>
         <v>0.59748555633329425</v>
       </c>
-      <c r="J321" s="6">
+      <c r="J321" s="1">
         <f>AVERAGE('RAUI-m'!J319:J321)</f>
         <v>0.48231249149632921</v>
       </c>
-      <c r="K321" s="6">
+      <c r="K321" s="1">
         <f>AVERAGE('RAUI-m'!K319:K321)</f>
         <v>8.9094973829200508E-2</v>
       </c>
-      <c r="L321" s="6">
+      <c r="L321" s="1">
         <f>AVERAGE('RAUI-m'!L319:L321)</f>
         <v>0.81846883083472577</v>
       </c>
@@ -29524,49 +29521,49 @@
       <c r="A322" t="s">
         <v>320</v>
       </c>
-      <c r="B322" s="6">
+      <c r="B322" s="1">
         <f>AVERAGE('RAUI-m'!B320:B322)</f>
-        <v>1.6190066615825689</v>
-      </c>
-      <c r="C322" s="6">
+        <v>1.3705083639847511</v>
+      </c>
+      <c r="C322" s="1">
         <f>AVERAGE('RAUI-m'!C320:C322)</f>
-        <v>1.5181853225985817</v>
-      </c>
-      <c r="D322" s="6">
+        <v>1.3747229098877491</v>
+      </c>
+      <c r="D322" s="1">
         <f>AVERAGE('RAUI-m'!D320:D322)</f>
-        <v>0.29806745562672399</v>
-      </c>
-      <c r="E322" s="6">
+        <v>0.20158160825540403</v>
+      </c>
+      <c r="E322" s="1">
         <f>AVERAGE('RAUI-m'!E320:E322)</f>
-        <v>0.49490276629316382</v>
-      </c>
-      <c r="F322" s="6">
+        <v>0.37689866661519916</v>
+      </c>
+      <c r="F322" s="1">
         <f>AVERAGE('RAUI-m'!F320:F322)</f>
-        <v>2.4400111482710241</v>
-      </c>
-      <c r="G322" s="6">
+        <v>2.3857610585904729</v>
+      </c>
+      <c r="G322" s="1">
         <f>AVERAGE('RAUI-m'!G320:G322)</f>
-        <v>1.3590343687070543</v>
-      </c>
-      <c r="H322" s="6">
+        <v>1.3466951799893672</v>
+      </c>
+      <c r="H322" s="1">
         <f>AVERAGE('RAUI-m'!H320:H322)</f>
-        <v>-0.82020162111017658</v>
-      </c>
-      <c r="I322" s="6">
+        <v>-0.9992615006410791</v>
+      </c>
+      <c r="I322" s="1">
         <f>AVERAGE('RAUI-m'!I320:I322)</f>
-        <v>0.58165009423069569</v>
-      </c>
-      <c r="J322" s="6">
+        <v>0.58865304864989898</v>
+      </c>
+      <c r="J322" s="1">
         <f>AVERAGE('RAUI-m'!J320:J322)</f>
-        <v>-1.6744042404981518E-2</v>
-      </c>
-      <c r="K322" s="6">
+        <v>0.87030923328069798</v>
+      </c>
+      <c r="K322" s="1">
         <f>AVERAGE('RAUI-m'!K320:K322)</f>
-        <v>2.5432050151293881E-2</v>
-      </c>
-      <c r="L322" s="6">
+        <v>6.3422064501174588E-2</v>
+      </c>
+      <c r="L322" s="1">
         <f>AVERAGE('RAUI-m'!L320:L322)</f>
-        <v>1.139830259285934</v>
+        <v>1.1289418086598124</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.35">
